--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596787</v>
+        <v>129597455</v>
       </c>
       <c r="B6" t="n">
-        <v>97598</v>
+        <v>78801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474009</v>
+        <v>474036</v>
       </c>
       <c r="R6" t="n">
-        <v>7024128</v>
+        <v>7024095</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,32 +1229,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129597455</v>
+        <v>129596787</v>
       </c>
       <c r="B7" t="n">
-        <v>78801</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474036</v>
+        <v>474009</v>
       </c>
       <c r="R7" t="n">
-        <v>7024095</v>
+        <v>7024128</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129596539</v>
+        <v>129596737</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,34 +1454,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473979</v>
+        <v>473984</v>
       </c>
       <c r="R9" t="n">
-        <v>7024153</v>
+        <v>7024114</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129596737</v>
+        <v>129597270</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>97068</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,39 +1566,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1841</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473984</v>
+        <v>474013</v>
       </c>
       <c r="R10" t="n">
-        <v>7024114</v>
+        <v>7024083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129597270</v>
+        <v>129596539</v>
       </c>
       <c r="B11" t="n">
-        <v>97068</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,21 +1673,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474013</v>
+        <v>473979</v>
       </c>
       <c r="R11" t="n">
-        <v>7024083</v>
+        <v>7024153</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2538,38 +2538,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129596012</v>
+        <v>129596823</v>
       </c>
       <c r="B19" t="n">
-        <v>105778</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473915</v>
+        <v>474011</v>
       </c>
       <c r="R19" t="n">
-        <v>7024160</v>
+        <v>7024151</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2623,7 +2623,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,38 +2655,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129596823</v>
+        <v>129596012</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>105778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2690,13 +2695,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474011</v>
+        <v>473915</v>
       </c>
       <c r="R20" t="n">
-        <v>7024151</v>
+        <v>7024160</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2725,7 +2730,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2735,12 +2740,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129597791</v>
+        <v>129596416</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474001</v>
+        <v>473984</v>
       </c>
       <c r="R3" t="n">
-        <v>7024159</v>
+        <v>7024143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129596449</v>
+        <v>129597791</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,39 +909,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473977</v>
+        <v>474001</v>
       </c>
       <c r="R4" t="n">
-        <v>7024133</v>
+        <v>7024159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,12 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetade/barkfläkta senvuxna granar.</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129596416</v>
+        <v>129596449</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,34 +1016,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473984</v>
+        <v>473977</v>
       </c>
       <c r="R5" t="n">
-        <v>7024143</v>
+        <v>7024133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetade/barkfläkta senvuxna granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129596737</v>
+        <v>129597270</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>97068</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,39 +1454,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1841</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473984</v>
+        <v>474013</v>
       </c>
       <c r="R9" t="n">
-        <v>7024114</v>
+        <v>7024083</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1528,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129597270</v>
+        <v>129596539</v>
       </c>
       <c r="B10" t="n">
-        <v>97068</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1590,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474013</v>
+        <v>473979</v>
       </c>
       <c r="R10" t="n">
-        <v>7024083</v>
+        <v>7024153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1635,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129596539</v>
+        <v>129596737</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,34 +1668,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473979</v>
+        <v>473984</v>
       </c>
       <c r="R11" t="n">
-        <v>7024153</v>
+        <v>7024114</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597599</v>
+        <v>129597595</v>
       </c>
       <c r="B13" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597449</v>
+        <v>129597599</v>
       </c>
       <c r="B14" t="n">
         <v>79663</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R14" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597595</v>
+        <v>129597449</v>
       </c>
       <c r="B15" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R15" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2180,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129596416</v>
+        <v>129596449</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473984</v>
+        <v>473977</v>
       </c>
       <c r="R3" t="n">
-        <v>7024143</v>
+        <v>7024133</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetade/barkfläkta senvuxna granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129597791</v>
+        <v>129596416</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -933,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474001</v>
+        <v>473984</v>
       </c>
       <c r="R4" t="n">
-        <v>7024159</v>
+        <v>7024143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129596449</v>
+        <v>129597791</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,39 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473977</v>
+        <v>474001</v>
       </c>
       <c r="R5" t="n">
-        <v>7024133</v>
+        <v>7024159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetade/barkfläkta senvuxna granar.</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129597455</v>
+        <v>129596296</v>
       </c>
       <c r="B6" t="n">
-        <v>78801</v>
+        <v>91553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474036</v>
+        <v>473965</v>
       </c>
       <c r="R6" t="n">
-        <v>7024095</v>
+        <v>7024119</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,32 +1229,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596787</v>
+        <v>129597455</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>78801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474009</v>
+        <v>474036</v>
       </c>
       <c r="R7" t="n">
-        <v>7024128</v>
+        <v>7024095</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596296</v>
+        <v>129596787</v>
       </c>
       <c r="B8" t="n">
-        <v>91553</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473965</v>
+        <v>474009</v>
       </c>
       <c r="R8" t="n">
-        <v>7024119</v>
+        <v>7024128</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597595</v>
+        <v>129597599</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597599</v>
+        <v>129597449</v>
       </c>
       <c r="B14" t="n">
         <v>79663</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R14" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2073,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597449</v>
+        <v>129597595</v>
       </c>
       <c r="B15" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,21 +2116,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R15" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,12 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2538,38 +2538,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129596823</v>
+        <v>129596012</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>105778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474011</v>
+        <v>473915</v>
       </c>
       <c r="R19" t="n">
-        <v>7024151</v>
+        <v>7024160</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2623,12 +2623,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,38 +2650,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129596012</v>
+        <v>129596823</v>
       </c>
       <c r="B20" t="n">
-        <v>105778</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2695,13 +2690,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473915</v>
+        <v>474011</v>
       </c>
       <c r="R20" t="n">
-        <v>7024160</v>
+        <v>7024151</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2730,7 +2725,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2740,7 +2735,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129596449</v>
+        <v>129596416</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473977</v>
+        <v>473984</v>
       </c>
       <c r="R3" t="n">
-        <v>7024133</v>
+        <v>7024143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetade/barkfläkta senvuxna granar.</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129596416</v>
+        <v>129597791</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -943,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473984</v>
+        <v>474001</v>
       </c>
       <c r="R4" t="n">
-        <v>7024143</v>
+        <v>7024159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129597791</v>
+        <v>129596449</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,34 +1016,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474001</v>
+        <v>473977</v>
       </c>
       <c r="R5" t="n">
-        <v>7024159</v>
+        <v>7024133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetade/barkfläkta senvuxna granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596296</v>
+        <v>129596787</v>
       </c>
       <c r="B6" t="n">
-        <v>91553</v>
+        <v>97598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473965</v>
+        <v>474009</v>
       </c>
       <c r="R6" t="n">
-        <v>7024119</v>
+        <v>7024128</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129597455</v>
+        <v>129596296</v>
       </c>
       <c r="B7" t="n">
-        <v>78801</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474036</v>
+        <v>473965</v>
       </c>
       <c r="R7" t="n">
-        <v>7024095</v>
+        <v>7024119</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596787</v>
+        <v>129597455</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>78801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474009</v>
+        <v>474036</v>
       </c>
       <c r="R8" t="n">
-        <v>7024128</v>
+        <v>7024095</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129597270</v>
+        <v>129596539</v>
       </c>
       <c r="B9" t="n">
-        <v>97068</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474013</v>
+        <v>473979</v>
       </c>
       <c r="R9" t="n">
-        <v>7024083</v>
+        <v>7024153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129596539</v>
+        <v>129597270</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>97068</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473979</v>
+        <v>474013</v>
       </c>
       <c r="R10" t="n">
-        <v>7024153</v>
+        <v>7024083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597599</v>
+        <v>129597595</v>
       </c>
       <c r="B13" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597449</v>
+        <v>129597599</v>
       </c>
       <c r="B14" t="n">
         <v>79663</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R14" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597595</v>
+        <v>129597449</v>
       </c>
       <c r="B15" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R15" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2180,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595940</v>
       </c>
       <c r="B2" t="n">
-        <v>105778</v>
+        <v>105807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129596416</v>
+        <v>129596449</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473984</v>
+        <v>473977</v>
       </c>
       <c r="R3" t="n">
-        <v>7024143</v>
+        <v>7024133</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetade/barkfläkta senvuxna granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129597791</v>
+        <v>129596416</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474001</v>
+        <v>473984</v>
       </c>
       <c r="R4" t="n">
-        <v>7024159</v>
+        <v>7024143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129596449</v>
+        <v>129597791</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,39 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473977</v>
+        <v>474001</v>
       </c>
       <c r="R5" t="n">
-        <v>7024133</v>
+        <v>7024159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetade/barkfläkta senvuxna granar.</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596787</v>
+        <v>129596296</v>
       </c>
       <c r="B6" t="n">
-        <v>97598</v>
+        <v>91581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474009</v>
+        <v>473965</v>
       </c>
       <c r="R6" t="n">
-        <v>7024128</v>
+        <v>7024119</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596296</v>
+        <v>129597455</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>78827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473965</v>
+        <v>474036</v>
       </c>
       <c r="R7" t="n">
-        <v>7024119</v>
+        <v>7024095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129597455</v>
+        <v>129596787</v>
       </c>
       <c r="B8" t="n">
-        <v>78801</v>
+        <v>97627</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474036</v>
+        <v>474009</v>
       </c>
       <c r="R8" t="n">
-        <v>7024095</v>
+        <v>7024128</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129596539</v>
+        <v>129597270</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>97097</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473979</v>
+        <v>474013</v>
       </c>
       <c r="R9" t="n">
-        <v>7024153</v>
+        <v>7024083</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129597270</v>
+        <v>129596539</v>
       </c>
       <c r="B10" t="n">
-        <v>97068</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474013</v>
+        <v>473979</v>
       </c>
       <c r="R10" t="n">
-        <v>7024083</v>
+        <v>7024153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,7 +1660,7 @@
         <v>129596737</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597595</v>
+        <v>129597599</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>79689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597599</v>
+        <v>129597449</v>
       </c>
       <c r="B14" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R14" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2073,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597449</v>
+        <v>129597595</v>
       </c>
       <c r="B15" t="n">
-        <v>79663</v>
+        <v>78828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,21 +2116,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R15" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,12 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
         <v>129596207</v>
       </c>
       <c r="B16" t="n">
-        <v>105778</v>
+        <v>105807</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129597587</v>
       </c>
       <c r="B17" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>129598113</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,38 +2538,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129596012</v>
+        <v>129596823</v>
       </c>
       <c r="B19" t="n">
-        <v>105778</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473915</v>
+        <v>474011</v>
       </c>
       <c r="R19" t="n">
-        <v>7024160</v>
+        <v>7024151</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2623,7 +2623,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,38 +2655,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129596823</v>
+        <v>129596012</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>105807</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2690,13 +2695,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474011</v>
+        <v>473915</v>
       </c>
       <c r="R20" t="n">
-        <v>7024151</v>
+        <v>7024160</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2725,7 +2730,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2735,12 +2740,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,7 +2770,7 @@
         <v>129597346</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129596202</v>
       </c>
       <c r="B22" t="n">
-        <v>98729</v>
+        <v>98758</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>129597703</v>
       </c>
       <c r="B23" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596296</v>
+        <v>129596787</v>
       </c>
       <c r="B6" t="n">
-        <v>91581</v>
+        <v>97627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473965</v>
+        <v>474009</v>
       </c>
       <c r="R6" t="n">
-        <v>7024119</v>
+        <v>7024128</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129597455</v>
+        <v>129596296</v>
       </c>
       <c r="B7" t="n">
-        <v>78827</v>
+        <v>91581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474036</v>
+        <v>473965</v>
       </c>
       <c r="R7" t="n">
-        <v>7024095</v>
+        <v>7024119</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596787</v>
+        <v>129597455</v>
       </c>
       <c r="B8" t="n">
-        <v>97627</v>
+        <v>78827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474009</v>
+        <v>474036</v>
       </c>
       <c r="R8" t="n">
-        <v>7024128</v>
+        <v>7024095</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595940</v>
       </c>
       <c r="B2" t="n">
-        <v>105807</v>
+        <v>105819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129596449</v>
+        <v>129596416</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473977</v>
+        <v>473984</v>
       </c>
       <c r="R3" t="n">
-        <v>7024133</v>
+        <v>7024143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetade/barkfläkta senvuxna granar.</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129596416</v>
+        <v>129597791</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473984</v>
+        <v>474001</v>
       </c>
       <c r="R4" t="n">
-        <v>7024143</v>
+        <v>7024159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129597791</v>
+        <v>129596449</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,34 +1016,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474001</v>
+        <v>473977</v>
       </c>
       <c r="R5" t="n">
-        <v>7024159</v>
+        <v>7024133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetade/barkfläkta senvuxna granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596787</v>
+        <v>129596296</v>
       </c>
       <c r="B6" t="n">
-        <v>97627</v>
+        <v>91587</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474009</v>
+        <v>473965</v>
       </c>
       <c r="R6" t="n">
-        <v>7024128</v>
+        <v>7024119</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596296</v>
+        <v>129597455</v>
       </c>
       <c r="B7" t="n">
-        <v>91581</v>
+        <v>78832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473965</v>
+        <v>474036</v>
       </c>
       <c r="R7" t="n">
-        <v>7024119</v>
+        <v>7024095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129597455</v>
+        <v>129596787</v>
       </c>
       <c r="B8" t="n">
-        <v>78827</v>
+        <v>97639</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474036</v>
+        <v>474009</v>
       </c>
       <c r="R8" t="n">
-        <v>7024095</v>
+        <v>7024128</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,7 +1446,7 @@
         <v>129597270</v>
       </c>
       <c r="B9" t="n">
-        <v>97097</v>
+        <v>97109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>129596539</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>129596737</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597599</v>
+        <v>129597595</v>
       </c>
       <c r="B13" t="n">
-        <v>79689</v>
+        <v>78833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597449</v>
+        <v>129597599</v>
       </c>
       <c r="B14" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R14" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597595</v>
+        <v>129597449</v>
       </c>
       <c r="B15" t="n">
-        <v>78828</v>
+        <v>79694</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R15" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2180,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
         <v>129596207</v>
       </c>
       <c r="B16" t="n">
-        <v>105807</v>
+        <v>105819</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129597587</v>
       </c>
       <c r="B17" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>129598113</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129596823</v>
       </c>
       <c r="B19" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129596012</v>
       </c>
       <c r="B20" t="n">
-        <v>105807</v>
+        <v>105819</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>129597346</v>
       </c>
       <c r="B21" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129596202</v>
       </c>
       <c r="B22" t="n">
-        <v>98758</v>
+        <v>98770</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>129597703</v>
       </c>
       <c r="B23" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595940</v>
       </c>
       <c r="B2" t="n">
-        <v>105819</v>
+        <v>105820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129596416</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129597791</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129596449</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>129596296</v>
       </c>
       <c r="B6" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>129597455</v>
       </c>
       <c r="B7" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>129596787</v>
       </c>
       <c r="B8" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>129597270</v>
       </c>
       <c r="B9" t="n">
-        <v>97109</v>
+        <v>97110</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>129596539</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>129596737</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597595</v>
+        <v>129597599</v>
       </c>
       <c r="B13" t="n">
-        <v>78833</v>
+        <v>79695</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597599</v>
+        <v>129597449</v>
       </c>
       <c r="B14" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R14" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2073,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597449</v>
+        <v>129597595</v>
       </c>
       <c r="B15" t="n">
-        <v>79694</v>
+        <v>78834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,21 +2116,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R15" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,12 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
         <v>129596207</v>
       </c>
       <c r="B16" t="n">
-        <v>105819</v>
+        <v>105820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129597587</v>
       </c>
       <c r="B17" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>129598113</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129596823</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129596012</v>
       </c>
       <c r="B20" t="n">
-        <v>105819</v>
+        <v>105820</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>129597346</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129596202</v>
       </c>
       <c r="B22" t="n">
-        <v>98770</v>
+        <v>98771</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>129597703</v>
       </c>
       <c r="B23" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596296</v>
+        <v>129596787</v>
       </c>
       <c r="B6" t="n">
-        <v>91588</v>
+        <v>97640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473965</v>
+        <v>474009</v>
       </c>
       <c r="R6" t="n">
-        <v>7024119</v>
+        <v>7024128</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129597455</v>
+        <v>129596296</v>
       </c>
       <c r="B7" t="n">
-        <v>78833</v>
+        <v>91588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474036</v>
+        <v>473965</v>
       </c>
       <c r="R7" t="n">
-        <v>7024095</v>
+        <v>7024119</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596787</v>
+        <v>129597455</v>
       </c>
       <c r="B8" t="n">
-        <v>97640</v>
+        <v>78833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474009</v>
+        <v>474036</v>
       </c>
       <c r="R8" t="n">
-        <v>7024128</v>
+        <v>7024095</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595940</v>
       </c>
       <c r="B2" t="n">
-        <v>105820</v>
+        <v>105825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129596416</v>
+        <v>129596449</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473984</v>
+        <v>473977</v>
       </c>
       <c r="R3" t="n">
-        <v>7024143</v>
+        <v>7024133</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetade/barkfläkta senvuxna granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129597791</v>
+        <v>129596416</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474001</v>
+        <v>473984</v>
       </c>
       <c r="R4" t="n">
-        <v>7024159</v>
+        <v>7024143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129596449</v>
+        <v>129597791</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,39 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473977</v>
+        <v>474001</v>
       </c>
       <c r="R5" t="n">
-        <v>7024133</v>
+        <v>7024159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetade/barkfläkta senvuxna granar.</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596787</v>
+        <v>129596296</v>
       </c>
       <c r="B6" t="n">
-        <v>97640</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474009</v>
+        <v>473965</v>
       </c>
       <c r="R6" t="n">
-        <v>7024128</v>
+        <v>7024119</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596296</v>
+        <v>129597455</v>
       </c>
       <c r="B7" t="n">
-        <v>91588</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473965</v>
+        <v>474036</v>
       </c>
       <c r="R7" t="n">
-        <v>7024119</v>
+        <v>7024095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129597455</v>
+        <v>129596787</v>
       </c>
       <c r="B8" t="n">
-        <v>78833</v>
+        <v>97645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474036</v>
+        <v>474009</v>
       </c>
       <c r="R8" t="n">
-        <v>7024095</v>
+        <v>7024128</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,7 +1446,7 @@
         <v>129597270</v>
       </c>
       <c r="B9" t="n">
-        <v>97110</v>
+        <v>97115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>129596539</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597599</v>
+        <v>129597595</v>
       </c>
       <c r="B13" t="n">
-        <v>79695</v>
+        <v>78839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597449</v>
+        <v>129597599</v>
       </c>
       <c r="B14" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R14" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597595</v>
+        <v>129597449</v>
       </c>
       <c r="B15" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R15" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2180,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
         <v>129596207</v>
       </c>
       <c r="B16" t="n">
-        <v>105820</v>
+        <v>105825</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129597587</v>
       </c>
       <c r="B17" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>129598113</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129596012</v>
       </c>
       <c r="B20" t="n">
-        <v>105820</v>
+        <v>105825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129596202</v>
       </c>
       <c r="B22" t="n">
-        <v>98771</v>
+        <v>98776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>129597703</v>
       </c>
       <c r="B23" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -1229,32 +1229,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129597455</v>
+        <v>129596787</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>97645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474036</v>
+        <v>474009</v>
       </c>
       <c r="R7" t="n">
-        <v>7024095</v>
+        <v>7024128</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596787</v>
+        <v>129597455</v>
       </c>
       <c r="B8" t="n">
-        <v>97645</v>
+        <v>78838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474009</v>
+        <v>474036</v>
       </c>
       <c r="R8" t="n">
-        <v>7024128</v>
+        <v>7024095</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129597270</v>
+        <v>129596539</v>
       </c>
       <c r="B9" t="n">
-        <v>97115</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474013</v>
+        <v>473979</v>
       </c>
       <c r="R9" t="n">
-        <v>7024083</v>
+        <v>7024153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129596539</v>
+        <v>129597270</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>97115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473979</v>
+        <v>474013</v>
       </c>
       <c r="R10" t="n">
-        <v>7024153</v>
+        <v>7024083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597595</v>
+        <v>129597599</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597599</v>
+        <v>129597449</v>
       </c>
       <c r="B14" t="n">
         <v>79700</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R14" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2073,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597449</v>
+        <v>129597595</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,21 +2116,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R15" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,12 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129596449</v>
+        <v>129596416</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473977</v>
+        <v>473984</v>
       </c>
       <c r="R3" t="n">
-        <v>7024133</v>
+        <v>7024143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetade/barkfläkta senvuxna granar.</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129596416</v>
+        <v>129597791</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -943,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473984</v>
+        <v>474001</v>
       </c>
       <c r="R4" t="n">
-        <v>7024143</v>
+        <v>7024159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129597791</v>
+        <v>129596449</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,34 +1016,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474001</v>
+        <v>473977</v>
       </c>
       <c r="R5" t="n">
-        <v>7024159</v>
+        <v>7024133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetade/barkfläkta senvuxna granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1229,32 +1229,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596787</v>
+        <v>129597455</v>
       </c>
       <c r="B7" t="n">
-        <v>97645</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474009</v>
+        <v>474036</v>
       </c>
       <c r="R7" t="n">
-        <v>7024128</v>
+        <v>7024095</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129597455</v>
+        <v>129596787</v>
       </c>
       <c r="B8" t="n">
-        <v>78838</v>
+        <v>97645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474036</v>
+        <v>474009</v>
       </c>
       <c r="R8" t="n">
-        <v>7024095</v>
+        <v>7024128</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129596539</v>
+        <v>129597270</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>97115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473979</v>
+        <v>474013</v>
       </c>
       <c r="R9" t="n">
-        <v>7024153</v>
+        <v>7024083</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129597270</v>
+        <v>129596539</v>
       </c>
       <c r="B10" t="n">
-        <v>97115</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474013</v>
+        <v>473979</v>
       </c>
       <c r="R10" t="n">
-        <v>7024083</v>
+        <v>7024153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2538,38 +2538,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129596823</v>
+        <v>129596012</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>105825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474011</v>
+        <v>473915</v>
       </c>
       <c r="R19" t="n">
-        <v>7024151</v>
+        <v>7024160</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2623,12 +2623,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,38 +2650,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129596012</v>
+        <v>129596823</v>
       </c>
       <c r="B20" t="n">
-        <v>105825</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2695,13 +2690,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473915</v>
+        <v>474011</v>
       </c>
       <c r="R20" t="n">
-        <v>7024160</v>
+        <v>7024151</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2730,7 +2725,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2740,7 +2735,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596296</v>
+        <v>129596787</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>97645</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473965</v>
+        <v>474009</v>
       </c>
       <c r="R6" t="n">
-        <v>7024119</v>
+        <v>7024128</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129597455</v>
+        <v>129596296</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>91593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474036</v>
+        <v>473965</v>
       </c>
       <c r="R7" t="n">
-        <v>7024095</v>
+        <v>7024119</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596787</v>
+        <v>129597455</v>
       </c>
       <c r="B8" t="n">
-        <v>97645</v>
+        <v>78838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474009</v>
+        <v>474036</v>
       </c>
       <c r="R8" t="n">
-        <v>7024128</v>
+        <v>7024095</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129597270</v>
+        <v>129596737</v>
       </c>
       <c r="B9" t="n">
-        <v>97115</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,34 +1454,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1841</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474013</v>
+        <v>473984</v>
       </c>
       <c r="R9" t="n">
-        <v>7024083</v>
+        <v>7024114</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1518,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1528,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129596539</v>
+        <v>129597270</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>97115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1566,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473979</v>
+        <v>474013</v>
       </c>
       <c r="R10" t="n">
-        <v>7024153</v>
+        <v>7024083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1625,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1635,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129596737</v>
+        <v>129596539</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,39 +1673,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473984</v>
+        <v>473979</v>
       </c>
       <c r="R11" t="n">
-        <v>7024114</v>
+        <v>7024153</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597599</v>
+        <v>129597595</v>
       </c>
       <c r="B13" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597449</v>
+        <v>129597599</v>
       </c>
       <c r="B14" t="n">
         <v>79700</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R14" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2073,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597595</v>
+        <v>129597449</v>
       </c>
       <c r="B15" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2140,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R15" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2180,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2538,38 +2538,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129596012</v>
+        <v>129596823</v>
       </c>
       <c r="B19" t="n">
-        <v>105825</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473915</v>
+        <v>474011</v>
       </c>
       <c r="R19" t="n">
-        <v>7024160</v>
+        <v>7024151</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2623,7 +2623,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,38 +2655,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129596823</v>
+        <v>129596012</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>105825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2690,13 +2695,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474011</v>
+        <v>473915</v>
       </c>
       <c r="R20" t="n">
-        <v>7024151</v>
+        <v>7024160</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2725,7 +2730,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2735,12 +2740,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595940</v>
       </c>
       <c r="B2" t="n">
-        <v>105825</v>
+        <v>105829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129596416</v>
+        <v>129596449</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473984</v>
+        <v>473977</v>
       </c>
       <c r="R3" t="n">
-        <v>7024143</v>
+        <v>7024133</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetade/barkfläkta senvuxna granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129597791</v>
+        <v>129596416</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -933,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474001</v>
+        <v>473984</v>
       </c>
       <c r="R4" t="n">
-        <v>7024159</v>
+        <v>7024143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129596449</v>
+        <v>129597791</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,39 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473977</v>
+        <v>474001</v>
       </c>
       <c r="R5" t="n">
-        <v>7024133</v>
+        <v>7024159</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetade/barkfläkta senvuxna granar.</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596787</v>
+        <v>129596296</v>
       </c>
       <c r="B6" t="n">
-        <v>97645</v>
+        <v>91597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474009</v>
+        <v>473965</v>
       </c>
       <c r="R6" t="n">
-        <v>7024128</v>
+        <v>7024119</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596296</v>
+        <v>129597455</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473965</v>
+        <v>474036</v>
       </c>
       <c r="R7" t="n">
-        <v>7024119</v>
+        <v>7024095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129597455</v>
+        <v>129596787</v>
       </c>
       <c r="B8" t="n">
-        <v>78838</v>
+        <v>97649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474036</v>
+        <v>474009</v>
       </c>
       <c r="R8" t="n">
-        <v>7024095</v>
+        <v>7024128</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1558,7 +1558,7 @@
         <v>129597270</v>
       </c>
       <c r="B10" t="n">
-        <v>97115</v>
+        <v>97119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597595</v>
+        <v>129597599</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597599</v>
+        <v>129597449</v>
       </c>
       <c r="B14" t="n">
         <v>79700</v>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R14" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2073,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597449</v>
+        <v>129597595</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,21 +2116,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R15" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,12 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
         <v>129596207</v>
       </c>
       <c r="B16" t="n">
-        <v>105825</v>
+        <v>105829</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129596012</v>
       </c>
       <c r="B20" t="n">
-        <v>105825</v>
+        <v>105829</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129596202</v>
       </c>
       <c r="B22" t="n">
-        <v>98776</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595940</v>
       </c>
       <c r="B2" t="n">
-        <v>105829</v>
+        <v>105831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129596416</v>
+        <v>129597791</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473984</v>
+        <v>474001</v>
       </c>
       <c r="R4" t="n">
-        <v>7024143</v>
+        <v>7024159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129597791</v>
+        <v>129596416</v>
       </c>
       <c r="B5" t="n">
         <v>79081</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474001</v>
+        <v>473984</v>
       </c>
       <c r="R5" t="n">
-        <v>7024159</v>
+        <v>7024143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596296</v>
+        <v>129596787</v>
       </c>
       <c r="B6" t="n">
-        <v>91597</v>
+        <v>97651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473965</v>
+        <v>474009</v>
       </c>
       <c r="R6" t="n">
-        <v>7024119</v>
+        <v>7024128</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129597455</v>
+        <v>129596296</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>91599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474036</v>
+        <v>473965</v>
       </c>
       <c r="R7" t="n">
-        <v>7024095</v>
+        <v>7024119</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596787</v>
+        <v>129597455</v>
       </c>
       <c r="B8" t="n">
-        <v>97649</v>
+        <v>78838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474009</v>
+        <v>474036</v>
       </c>
       <c r="R8" t="n">
-        <v>7024128</v>
+        <v>7024095</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129597270</v>
+        <v>129596539</v>
       </c>
       <c r="B10" t="n">
-        <v>97119</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,21 +1566,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474013</v>
+        <v>473979</v>
       </c>
       <c r="R10" t="n">
-        <v>7024083</v>
+        <v>7024153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129596539</v>
+        <v>129597270</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>97121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,21 +1673,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473979</v>
+        <v>474013</v>
       </c>
       <c r="R11" t="n">
-        <v>7024153</v>
+        <v>7024083</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2215,7 +2215,7 @@
         <v>129596207</v>
       </c>
       <c r="B16" t="n">
-        <v>105829</v>
+        <v>105831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129596012</v>
       </c>
       <c r="B20" t="n">
-        <v>105829</v>
+        <v>105831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129596202</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>98782</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596787</v>
+        <v>129596296</v>
       </c>
       <c r="B6" t="n">
-        <v>97651</v>
+        <v>91599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474009</v>
+        <v>473965</v>
       </c>
       <c r="R6" t="n">
-        <v>7024128</v>
+        <v>7024119</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596296</v>
+        <v>129597455</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473965</v>
+        <v>474036</v>
       </c>
       <c r="R7" t="n">
-        <v>7024119</v>
+        <v>7024095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129597455</v>
+        <v>129596787</v>
       </c>
       <c r="B8" t="n">
-        <v>78838</v>
+        <v>97651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474036</v>
+        <v>474009</v>
       </c>
       <c r="R8" t="n">
-        <v>7024095</v>
+        <v>7024128</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129596449</v>
+        <v>129597791</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473977</v>
+        <v>474001</v>
       </c>
       <c r="R3" t="n">
-        <v>7024133</v>
+        <v>7024159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetade/barkfläkta senvuxna granar.</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129597791</v>
+        <v>129596416</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -943,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474001</v>
+        <v>473984</v>
       </c>
       <c r="R4" t="n">
-        <v>7024159</v>
+        <v>7024143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129596416</v>
+        <v>129596449</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,34 +1016,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473984</v>
+        <v>473977</v>
       </c>
       <c r="R5" t="n">
-        <v>7024143</v>
+        <v>7024133</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1090,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetade/barkfläkta senvuxna granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595940</v>
       </c>
       <c r="B2" t="n">
-        <v>105831</v>
+        <v>105841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596296</v>
+        <v>129597455</v>
       </c>
       <c r="B6" t="n">
-        <v>91599</v>
+        <v>78838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473965</v>
+        <v>474036</v>
       </c>
       <c r="R6" t="n">
-        <v>7024119</v>
+        <v>7024095</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129597455</v>
+        <v>129596296</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>91599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474036</v>
+        <v>473965</v>
       </c>
       <c r="R7" t="n">
-        <v>7024095</v>
+        <v>7024119</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,7 +1339,7 @@
         <v>129596787</v>
       </c>
       <c r="B8" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129596737</v>
+        <v>129596539</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,39 +1454,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473984</v>
+        <v>473979</v>
       </c>
       <c r="R9" t="n">
-        <v>7024114</v>
+        <v>7024153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129596539</v>
+        <v>129597270</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>97131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,21 +1561,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1590,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473979</v>
+        <v>474013</v>
       </c>
       <c r="R10" t="n">
-        <v>7024153</v>
+        <v>7024083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1635,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129597270</v>
+        <v>129596737</v>
       </c>
       <c r="B11" t="n">
-        <v>97121</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,34 +1668,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1841</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474013</v>
+        <v>473984</v>
       </c>
       <c r="R11" t="n">
-        <v>7024083</v>
+        <v>7024114</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2215,7 +2215,7 @@
         <v>129596207</v>
       </c>
       <c r="B16" t="n">
-        <v>105831</v>
+        <v>105841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2538,38 +2538,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129596823</v>
+        <v>129596012</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>105841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474011</v>
+        <v>473915</v>
       </c>
       <c r="R19" t="n">
-        <v>7024151</v>
+        <v>7024160</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2623,12 +2623,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,38 +2650,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129596012</v>
+        <v>129596823</v>
       </c>
       <c r="B20" t="n">
-        <v>105831</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2695,13 +2690,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473915</v>
+        <v>474011</v>
       </c>
       <c r="R20" t="n">
-        <v>7024160</v>
+        <v>7024151</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2730,7 +2725,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2740,7 +2735,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,7 +2887,7 @@
         <v>129596202</v>
       </c>
       <c r="B22" t="n">
-        <v>98782</v>
+        <v>98792</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129597455</v>
+        <v>129596787</v>
       </c>
       <c r="B6" t="n">
-        <v>78838</v>
+        <v>97661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474036</v>
+        <v>474009</v>
       </c>
       <c r="R6" t="n">
-        <v>7024095</v>
+        <v>7024128</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596296</v>
+        <v>129597455</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473965</v>
+        <v>474036</v>
       </c>
       <c r="R7" t="n">
-        <v>7024119</v>
+        <v>7024095</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596787</v>
+        <v>129596296</v>
       </c>
       <c r="B8" t="n">
-        <v>97661</v>
+        <v>91599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474009</v>
+        <v>473965</v>
       </c>
       <c r="R8" t="n">
-        <v>7024128</v>
+        <v>7024119</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129596539</v>
+        <v>129596737</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,34 +1454,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473979</v>
+        <v>473984</v>
       </c>
       <c r="R9" t="n">
-        <v>7024153</v>
+        <v>7024114</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129597270</v>
+        <v>129596539</v>
       </c>
       <c r="B10" t="n">
-        <v>97131</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1566,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474013</v>
+        <v>473979</v>
       </c>
       <c r="R10" t="n">
-        <v>7024083</v>
+        <v>7024153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1625,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1635,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129596737</v>
+        <v>129597270</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>97131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,39 +1673,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1841</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473984</v>
+        <v>474013</v>
       </c>
       <c r="R11" t="n">
-        <v>7024114</v>
+        <v>7024083</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595940</v>
       </c>
       <c r="B2" t="n">
-        <v>105841</v>
+        <v>105845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129597791</v>
+        <v>129596416</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474001</v>
+        <v>473984</v>
       </c>
       <c r="R3" t="n">
-        <v>7024159</v>
+        <v>7024143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129596416</v>
+        <v>129597791</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473984</v>
+        <v>474001</v>
       </c>
       <c r="R4" t="n">
-        <v>7024143</v>
+        <v>7024159</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +1008,7 @@
         <v>129596449</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,32 +1122,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596787</v>
+        <v>129597455</v>
       </c>
       <c r="B6" t="n">
-        <v>97661</v>
+        <v>78841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474009</v>
+        <v>474036</v>
       </c>
       <c r="R6" t="n">
-        <v>7024128</v>
+        <v>7024095</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129597455</v>
+        <v>129596296</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>91602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474036</v>
+        <v>473965</v>
       </c>
       <c r="R7" t="n">
-        <v>7024095</v>
+        <v>7024119</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596296</v>
+        <v>129596787</v>
       </c>
       <c r="B8" t="n">
-        <v>91599</v>
+        <v>97665</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473965</v>
+        <v>474009</v>
       </c>
       <c r="R8" t="n">
-        <v>7024119</v>
+        <v>7024128</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129596737</v>
+        <v>129596539</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,39 +1454,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473984</v>
+        <v>473979</v>
       </c>
       <c r="R9" t="n">
-        <v>7024114</v>
+        <v>7024153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129596539</v>
+        <v>129596737</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,34 +1561,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473979</v>
+        <v>473984</v>
       </c>
       <c r="R10" t="n">
-        <v>7024153</v>
+        <v>7024114</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
         <v>129597270</v>
       </c>
       <c r="B11" t="n">
-        <v>97131</v>
+        <v>97135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597599</v>
+        <v>129597449</v>
       </c>
       <c r="B13" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R13" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1966,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,10 +1998,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597449</v>
+        <v>129597595</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>78842</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,21 +2009,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2028,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R14" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2068,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2078,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597595</v>
+        <v>129597599</v>
       </c>
       <c r="B15" t="n">
-        <v>78839</v>
+        <v>79703</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,21 +2116,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
         <v>129596207</v>
       </c>
       <c r="B16" t="n">
-        <v>105841</v>
+        <v>105845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129597587</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>129598113</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129596012</v>
       </c>
       <c r="B19" t="n">
-        <v>105841</v>
+        <v>105845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>129596823</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>129597346</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129596202</v>
       </c>
       <c r="B22" t="n">
-        <v>98792</v>
+        <v>98796</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>129597703</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -1229,32 +1229,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596296</v>
+        <v>129596787</v>
       </c>
       <c r="B7" t="n">
-        <v>91602</v>
+        <v>97665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473965</v>
+        <v>474009</v>
       </c>
       <c r="R7" t="n">
-        <v>7024119</v>
+        <v>7024128</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596787</v>
+        <v>129596296</v>
       </c>
       <c r="B8" t="n">
-        <v>97665</v>
+        <v>91602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474009</v>
+        <v>473965</v>
       </c>
       <c r="R8" t="n">
-        <v>7024128</v>
+        <v>7024119</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597449</v>
+        <v>129597595</v>
       </c>
       <c r="B13" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R13" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,12 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597595</v>
+        <v>129597599</v>
       </c>
       <c r="B14" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,21 +2004,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,7 +2100,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597599</v>
+        <v>129597449</v>
       </c>
       <c r="B15" t="n">
         <v>79703</v>
@@ -2140,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R15" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2170,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2180,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2538,38 +2538,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129596012</v>
+        <v>129596823</v>
       </c>
       <c r="B19" t="n">
-        <v>105845</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473915</v>
+        <v>474011</v>
       </c>
       <c r="R19" t="n">
-        <v>7024160</v>
+        <v>7024151</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2623,7 +2623,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,38 +2655,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129596823</v>
+        <v>129596012</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>105845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2690,13 +2695,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474011</v>
+        <v>473915</v>
       </c>
       <c r="R20" t="n">
-        <v>7024151</v>
+        <v>7024160</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2725,7 +2730,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2735,12 +2740,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129595940</v>
       </c>
       <c r="B2" t="n">
-        <v>105845</v>
+        <v>105848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>129596416</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>129597791</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>129596449</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129597455</v>
+        <v>129596296</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>91605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474036</v>
+        <v>473965</v>
       </c>
       <c r="R6" t="n">
-        <v>7024095</v>
+        <v>7024119</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
         <v>129596787</v>
       </c>
       <c r="B7" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129596296</v>
+        <v>129597455</v>
       </c>
       <c r="B8" t="n">
-        <v>91602</v>
+        <v>78844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473965</v>
+        <v>474036</v>
       </c>
       <c r="R8" t="n">
-        <v>7024119</v>
+        <v>7024095</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,7 +1446,7 @@
         <v>129596539</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129596737</v>
+        <v>129597270</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>97138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,39 +1561,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1841</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473984</v>
+        <v>474013</v>
       </c>
       <c r="R10" t="n">
-        <v>7024114</v>
+        <v>7024083</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1635,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1662,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129597270</v>
+        <v>129596737</v>
       </c>
       <c r="B11" t="n">
-        <v>97135</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,34 +1668,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1841</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>474013</v>
+        <v>473984</v>
       </c>
       <c r="R11" t="n">
-        <v>7024083</v>
+        <v>7024114</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597595</v>
+        <v>129597599</v>
       </c>
       <c r="B13" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,21 +1897,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597599</v>
+        <v>129597449</v>
       </c>
       <c r="B14" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474059</v>
+        <v>474041</v>
       </c>
       <c r="R14" t="n">
-        <v>7024143</v>
+        <v>7024100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,7 +2073,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,10 +2105,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597449</v>
+        <v>129597595</v>
       </c>
       <c r="B15" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,21 +2116,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2135,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474041</v>
+        <v>474059</v>
       </c>
       <c r="R15" t="n">
-        <v>7024100</v>
+        <v>7024143</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,7 +2175,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2180,12 +2185,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,7 +2215,7 @@
         <v>129596207</v>
       </c>
       <c r="B16" t="n">
-        <v>105845</v>
+        <v>105848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>129597587</v>
       </c>
       <c r="B17" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>129598113</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>129596823</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>129596012</v>
       </c>
       <c r="B20" t="n">
-        <v>105845</v>
+        <v>105848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>129597346</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>129596202</v>
       </c>
       <c r="B22" t="n">
-        <v>98796</v>
+        <v>98799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>129597703</v>
       </c>
       <c r="B23" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129595940</v>
+        <v>129596296</v>
       </c>
       <c r="B2" t="n">
-        <v>105848</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473933</v>
+        <v>473965</v>
       </c>
       <c r="R2" t="n">
-        <v>7024174</v>
+        <v>7024119</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129596416</v>
+        <v>129597270</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>97453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1841</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473984</v>
+        <v>474013</v>
       </c>
       <c r="R3" t="n">
-        <v>7024143</v>
+        <v>7024083</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,14 +862,14 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -898,14 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129597791</v>
+        <v>129596092</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -933,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474001</v>
+        <v>473904</v>
       </c>
       <c r="R4" t="n">
-        <v>7024159</v>
+        <v>7024163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129596449</v>
+        <v>129596416</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473977</v>
+        <v>473984</v>
       </c>
       <c r="R5" t="n">
-        <v>7024133</v>
+        <v>7024143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetade/barkfläkta senvuxna granar.</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129596296</v>
+        <v>129596539</v>
       </c>
       <c r="B6" t="n">
-        <v>91605</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473965</v>
+        <v>473979</v>
       </c>
       <c r="R6" t="n">
-        <v>7024119</v>
+        <v>7024153</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129596787</v>
+        <v>129597791</v>
       </c>
       <c r="B7" t="n">
-        <v>97668</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474009</v>
+        <v>474001</v>
       </c>
       <c r="R7" t="n">
-        <v>7024128</v>
+        <v>7024159</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129597455</v>
+        <v>129598113</v>
       </c>
       <c r="B8" t="n">
-        <v>78844</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474036</v>
+        <v>473963</v>
       </c>
       <c r="R8" t="n">
-        <v>7024095</v>
+        <v>7024167</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1416,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129596539</v>
+        <v>129597455</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473979</v>
+        <v>474036</v>
       </c>
       <c r="R9" t="n">
-        <v>7024153</v>
+        <v>7024095</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1523,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129597270</v>
+        <v>129597587</v>
       </c>
       <c r="B10" t="n">
-        <v>97138</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1841</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>474013</v>
+        <v>474059</v>
       </c>
       <c r="R10" t="n">
-        <v>7024083</v>
+        <v>7024143</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,14 +1611,14 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1657,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129596737</v>
+        <v>129597449</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,39 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473984</v>
+        <v>474041</v>
       </c>
       <c r="R11" t="n">
-        <v>7024114</v>
+        <v>7024100</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1718,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,50 +1750,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129597404</v>
+        <v>129597599</v>
       </c>
       <c r="B12" t="n">
-        <v>5177</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474039</v>
+        <v>474059</v>
       </c>
       <c r="R12" t="n">
-        <v>7024102</v>
+        <v>7024143</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,12 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129597599</v>
+        <v>129597703</v>
       </c>
       <c r="B13" t="n">
-        <v>79706</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474059</v>
+        <v>474038</v>
       </c>
       <c r="R13" t="n">
-        <v>7024143</v>
+        <v>7024151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129597449</v>
+        <v>129597948</v>
       </c>
       <c r="B14" t="n">
-        <v>79706</v>
+        <v>58067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,37 +1975,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100090</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474041</v>
+        <v>474001</v>
       </c>
       <c r="R14" t="n">
-        <v>7024100</v>
+        <v>7024159</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2063,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2073,12 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2105,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129597595</v>
+        <v>129596041</v>
       </c>
       <c r="B15" t="n">
-        <v>78845</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,34 +2087,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474059</v>
+        <v>473905</v>
       </c>
       <c r="R15" t="n">
-        <v>7024143</v>
+        <v>7024159</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2185,7 +2161,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Barkfläk på klena senvuxna granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,38 +2193,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129596207</v>
+        <v>129596449</v>
       </c>
       <c r="B16" t="n">
-        <v>105848</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2252,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473962</v>
+        <v>473977</v>
       </c>
       <c r="R16" t="n">
-        <v>7024122</v>
+        <v>7024133</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2287,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2297,7 +2278,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bearbetade/barkfläkta senvuxna granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2324,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129597587</v>
+        <v>129596737</v>
       </c>
       <c r="B17" t="n">
-        <v>78844</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,34 +2321,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474059</v>
+        <v>473984</v>
       </c>
       <c r="R17" t="n">
-        <v>7024143</v>
+        <v>7024114</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2385,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2404,7 +2395,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129598113</v>
+        <v>129596823</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,34 +2433,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473963</v>
+        <v>474011</v>
       </c>
       <c r="R18" t="n">
-        <v>7024167</v>
+        <v>7024151</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,7 +2497,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2511,7 +2507,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2538,10 +2539,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129596823</v>
+        <v>129597346</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,10 +2579,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474011</v>
+        <v>474033</v>
       </c>
       <c r="R19" t="n">
-        <v>7024151</v>
+        <v>7024084</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2613,7 +2614,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2623,12 +2624,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Barkfläkta/bearbetad gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129596012</v>
+        <v>129597404</v>
       </c>
       <c r="B20" t="n">
-        <v>105848</v>
+        <v>5179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2666,27 +2667,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2695,13 +2696,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473915</v>
+        <v>474039</v>
       </c>
       <c r="R20" t="n">
-        <v>7024160</v>
+        <v>7024102</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2730,7 +2731,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2740,7 +2741,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,10 +2773,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129597346</v>
+        <v>129595783</v>
       </c>
       <c r="B21" t="n">
-        <v>57740</v>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2778,27 +2784,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2807,13 +2817,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>474033</v>
+        <v>473911</v>
       </c>
       <c r="R21" t="n">
-        <v>7024084</v>
+        <v>7024206</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2842,7 +2852,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2852,12 +2862,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Barkfläkta/bearbetad gran.</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,7 +2892,7 @@
         <v>129596202</v>
       </c>
       <c r="B22" t="n">
-        <v>98799</v>
+        <v>99120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3000,45 +3005,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129597703</v>
+        <v>129595940</v>
       </c>
       <c r="B23" t="n">
-        <v>79706</v>
+        <v>106228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>474038</v>
+        <v>473933</v>
       </c>
       <c r="R23" t="n">
-        <v>7024151</v>
+        <v>7024174</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3070,7 +3084,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3080,7 +3094,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3104,6 +3118,765 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129596012</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>473915</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7024160</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129596207</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106228</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>473962</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7024122</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129596052</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>473904</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7024163</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129596787</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>474009</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7024128</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129597595</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>474059</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7024143</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129595811</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>473912</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7024199</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129596866</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lomtjärnbäcken, Lomtjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>474012</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7024120</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49139-2025 artfynd.xlsx
+++ b/artfynd/A 49139-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597270</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596092</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596416</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596539</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597791</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129598113</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597455</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597587</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597449</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597599</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597703</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597948</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596041</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2307,6 +2382,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596449</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2419,6 +2499,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596737</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2536,6 +2621,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596823</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2653,6 +2743,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597346</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2770,6 +2865,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597404</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2886,6 +2986,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129595783</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3002,6 +3107,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596202</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3118,6 +3228,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129595940</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3230,6 +3345,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596012</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3342,6 +3462,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596207</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3449,6 +3574,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596052</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3556,6 +3686,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596787</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3663,6 +3798,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129597595</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3770,6 +3910,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129595811</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3877,8 +4022,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129596866</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>